--- a/R088.xlsx
+++ b/R088.xlsx
@@ -11,27 +11,33 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="46">
   <si>
     <t/>
   </si>
   <si>
+    <t>20056971</t>
+  </si>
+  <si>
+    <t>TUMBLER BUAVITA PCS</t>
+  </si>
+  <si>
+    <t>R088</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>PT</t>
+  </si>
+  <si>
     <t>20060469</t>
   </si>
   <si>
     <t>TAS COCA COLA</t>
   </si>
   <si>
-    <t>R088</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
     <t>2</t>
-  </si>
-  <si>
-    <t>PT</t>
   </si>
   <si>
     <t>20067618</t>
@@ -535,7 +541,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -580,170 +586,170 @@
         <v>4</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="F3" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="F4" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>16</v>
-      </c>
       <c r="F5" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="F6" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="F7" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="F8" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="F9" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="C10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F10" s="1" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -757,13 +763,13 @@
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -777,13 +783,13 @@
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -797,13 +803,13 @@
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -817,33 +823,33 @@
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="C15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -857,13 +863,33 @@
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/R088.xlsx
+++ b/R088.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="44">
   <si>
     <t/>
   </si>
   <si>
-    <t>20056971</t>
-  </si>
-  <si>
-    <t>TUMBLER BUAVITA PCS</t>
+    <t>20060469</t>
+  </si>
+  <si>
+    <t>TAS COCA COLA</t>
   </si>
   <si>
     <t>R088</t>
@@ -28,16 +28,10 @@
     <t>1</t>
   </si>
   <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>PT</t>
-  </si>
-  <si>
-    <t>20060469</t>
-  </si>
-  <si>
-    <t>TAS COCA COLA</t>
-  </si>
-  <si>
-    <t>2</t>
   </si>
   <si>
     <t>20067618</t>
@@ -541,7 +535,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -586,18 +580,18 @@
         <v>4</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>3</v>
@@ -606,18 +600,18 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -626,18 +620,18 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -646,18 +640,18 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -666,18 +660,18 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -686,18 +680,18 @@
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -706,18 +700,18 @@
         <v>4</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -726,30 +720,30 @@
         <v>4</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -763,13 +757,13 @@
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -783,13 +777,13 @@
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -803,13 +797,13 @@
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -823,33 +817,33 @@
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -863,33 +857,13 @@
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/R088.xlsx
+++ b/R088.xlsx
@@ -115,7 +115,7 @@
     <t>20141306</t>
   </si>
   <si>
-    <t>IDM COSMETIC HADIAH</t>
+    <t xml:space="preserve">IDM COSMETIC </t>
   </si>
   <si>
     <t>20139151</t>

--- a/R088.xlsx
+++ b/R088.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="46">
   <si>
     <t/>
   </si>
@@ -143,6 +143,12 @@
   </si>
   <si>
     <t>FIESTA STANDEE TREAS</t>
+  </si>
+  <si>
+    <t>20142688</t>
+  </si>
+  <si>
+    <t>FIESTA X TREASURE PC</t>
   </si>
 </sst>
 </file>
@@ -535,7 +541,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -866,6 +872,26 @@
         <v>10</v>
       </c>
     </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/R088.xlsx
+++ b/R088.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="46">
   <si>
     <t/>
   </si>
@@ -541,7 +541,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -549,10 +549,11 @@
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="3" customWidth="1"/>
     <col min="5" max="5" width="4" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="6" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -571,8 +572,14 @@
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -588,11 +595,11 @@
       <c r="E2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -608,11 +615,11 @@
       <c r="E3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H3" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
@@ -628,11 +635,11 @@
       <c r="E4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H4" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -648,11 +655,11 @@
       <c r="E5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H5" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>17</v>
       </c>
@@ -668,11 +675,11 @@
       <c r="E6" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H6" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>20</v>
       </c>
@@ -688,11 +695,11 @@
       <c r="E7" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F7" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H7" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>23</v>
       </c>
@@ -708,11 +715,11 @@
       <c r="E8" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F8" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H8" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>26</v>
       </c>
@@ -728,11 +735,11 @@
       <c r="E9" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F9" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H9" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>29</v>
       </c>
@@ -748,11 +755,11 @@
       <c r="E10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="H10" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>31</v>
       </c>
@@ -768,11 +775,11 @@
       <c r="E11" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="H11" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>33</v>
       </c>
@@ -788,11 +795,11 @@
       <c r="E12" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="H12" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>35</v>
       </c>
@@ -808,11 +815,11 @@
       <c r="E13" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F13" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H13" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>37</v>
       </c>
@@ -828,11 +835,11 @@
       <c r="E14" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="H14" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>40</v>
       </c>
@@ -848,11 +855,11 @@
       <c r="E15" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F15" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H15" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>42</v>
       </c>
@@ -868,11 +875,11 @@
       <c r="E16" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F16" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H16" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>44</v>
       </c>
@@ -888,7 +895,7 @@
       <c r="E17" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="H17" s="1" t="s">
         <v>10</v>
       </c>
     </row>

--- a/R088.xlsx
+++ b/R088.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="46">
   <si>
     <t/>
   </si>
@@ -541,7 +541,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -549,11 +549,10 @@
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="3" customWidth="1"/>
     <col min="5" max="5" width="4" customWidth="1"/>
-    <col min="6" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="11" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -572,14 +571,8 @@
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -595,11 +588,11 @@
       <c r="E2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -615,11 +608,11 @@
       <c r="E3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F3" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
@@ -635,11 +628,11 @@
       <c r="E4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H4" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F4" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -655,11 +648,11 @@
       <c r="E5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H5" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F5" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>17</v>
       </c>
@@ -675,11 +668,11 @@
       <c r="E6" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="H6" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F6" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>20</v>
       </c>
@@ -695,11 +688,11 @@
       <c r="E7" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="H7" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F7" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>23</v>
       </c>
@@ -715,11 +708,11 @@
       <c r="E8" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="H8" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F8" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>26</v>
       </c>
@@ -735,11 +728,11 @@
       <c r="E9" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="H9" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F9" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>29</v>
       </c>
@@ -755,11 +748,11 @@
       <c r="E10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H10" s="1" t="s">
+      <c r="F10" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>31</v>
       </c>
@@ -775,11 +768,11 @@
       <c r="E11" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H11" s="1" t="s">
+      <c r="F11" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>33</v>
       </c>
@@ -795,11 +788,11 @@
       <c r="E12" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H12" s="1" t="s">
+      <c r="F12" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>35</v>
       </c>
@@ -815,11 +808,11 @@
       <c r="E13" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H13" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F13" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>37</v>
       </c>
@@ -835,11 +828,11 @@
       <c r="E14" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H14" s="1" t="s">
+      <c r="F14" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>40</v>
       </c>
@@ -855,11 +848,11 @@
       <c r="E15" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H15" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F15" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>42</v>
       </c>
@@ -875,11 +868,11 @@
       <c r="E16" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H16" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F16" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>44</v>
       </c>
@@ -895,7 +888,7 @@
       <c r="E17" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H17" s="1" t="s">
+      <c r="F17" s="1" t="s">
         <v>10</v>
       </c>
     </row>

--- a/R088.xlsx
+++ b/R088.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="53">
   <si>
     <t/>
   </si>
@@ -98,6 +98,27 @@
   </si>
   <si>
     <t>13</t>
+  </si>
+  <si>
+    <t>20143786</t>
+  </si>
+  <si>
+    <t>RYCO BMB RDG 20G</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20143792</t>
+  </si>
+  <si>
+    <t>RYCO BMB OPR AYM 20G</t>
+  </si>
+  <si>
+    <t>15</t>
   </si>
   <si>
     <t>20076489</t>
@@ -541,7 +562,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -743,41 +764,41 @@
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>6</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -786,7 +807,7 @@
         <v>5</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>6</v>
@@ -794,50 +815,50 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>39</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
@@ -846,7 +867,7 @@
         <v>13</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>10</v>
@@ -854,10 +875,10 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
@@ -866,18 +887,18 @@
         <v>13</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
@@ -886,9 +907,49 @@
         <v>13</v>
       </c>
       <c r="E17" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="F19" s="1" t="s">
         <v>10</v>
       </c>
     </row>
